--- a/data/daily_measurements.xlsx
+++ b/data/daily_measurements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ruben/dev/duckweed-rmbe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13D0D180-6A0D-B141-A771-F20349C3FCF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA500D6-680D-0549-9E77-AF8CBEEFB068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="980" yWindow="1260" windowWidth="27840" windowHeight="16240" xr2:uid="{1AF4B679-1F14-8444-99BB-B7E1E6DBFAB9}"/>
   </bookViews>
@@ -457,6 +457,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BBE42C9-4347-6048-B2F8-34461A0CE087}">
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -605,7 +608,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2">
-        <v>46181.693055555559</v>
+        <v>46182.688888888886</v>
       </c>
       <c r="G6" s="1">
         <v>35.68</v>
@@ -631,7 +634,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>46181.693055555559</v>
+        <v>46182.688888888886</v>
       </c>
       <c r="G7" s="1">
         <v>30.27</v>
@@ -657,7 +660,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>46181.693055555559</v>
+        <v>46182.688888888886</v>
       </c>
       <c r="G8" s="1">
         <v>38.270000000000003</v>
@@ -683,7 +686,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>46181.693055555559</v>
+        <v>46182.688888888886</v>
       </c>
       <c r="G9" s="1">
         <v>53.24</v>
@@ -694,5 +697,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/data/daily_measurements.xlsx
+++ b/data/daily_measurements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ruben/dev/duckweed-rmbe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA500D6-680D-0549-9E77-AF8CBEEFB068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A6771B-1454-9748-BDB7-A93AE38D8989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="980" yWindow="1260" windowWidth="27840" windowHeight="16240" xr2:uid="{1AF4B679-1F14-8444-99BB-B7E1E6DBFAB9}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16740" xr2:uid="{1AF4B679-1F14-8444-99BB-B7E1E6DBFAB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="12">
   <si>
     <t>container_id</t>
   </si>
@@ -455,10 +455,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BBE42C9-4347-6048-B2F8-34461A0CE087}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -692,6 +692,110 @@
         <v>53.24</v>
       </c>
       <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2">
+        <v>46183.601388888892</v>
+      </c>
+      <c r="G10" s="1">
+        <v>49.92</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>46183.601388888892</v>
+      </c>
+      <c r="G11" s="1">
+        <v>46.21</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>46183.601388888892</v>
+      </c>
+      <c r="G12" s="1">
+        <v>23.82</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>8</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2">
+        <v>46183.601388888892</v>
+      </c>
+      <c r="G13" s="1">
+        <v>30.9</v>
+      </c>
+      <c r="H13" s="1">
         <v>0</v>
       </c>
     </row>

--- a/data/daily_measurements.xlsx
+++ b/data/daily_measurements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ruben/dev/duckweed-rmbe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A6771B-1454-9748-BDB7-A93AE38D8989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEDD8AE-0B8E-0241-9401-41950F5BF0EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16740" xr2:uid="{1AF4B679-1F14-8444-99BB-B7E1E6DBFAB9}"/>
+    <workbookView xWindow="14700" yWindow="760" windowWidth="14700" windowHeight="16740" xr2:uid="{1AF4B679-1F14-8444-99BB-B7E1E6DBFAB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -507,7 +507,7 @@
         <v>46181.693055555559</v>
       </c>
       <c r="G2" s="1">
-        <v>27.24</v>
+        <v>36.450000000000003</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -533,7 +533,7 @@
         <v>46181.693055555559</v>
       </c>
       <c r="G3" s="1">
-        <v>36.799999999999997</v>
+        <v>51.17</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -559,7 +559,7 @@
         <v>46181.693055555559</v>
       </c>
       <c r="G4" s="1">
-        <v>16.420000000000002</v>
+        <v>27.15</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -585,7 +585,7 @@
         <v>46181.693055555559</v>
       </c>
       <c r="G5" s="1">
-        <v>32.42</v>
+        <v>37.04</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -611,7 +611,7 @@
         <v>46182.688888888886</v>
       </c>
       <c r="G6" s="1">
-        <v>35.68</v>
+        <v>55.96</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -637,7 +637,7 @@
         <v>46182.688888888886</v>
       </c>
       <c r="G7" s="1">
-        <v>30.27</v>
+        <v>46.87</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -663,7 +663,7 @@
         <v>46182.688888888886</v>
       </c>
       <c r="G8" s="1">
-        <v>38.270000000000003</v>
+        <v>56.96</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>46182.688888888886</v>
       </c>
       <c r="G9" s="1">
-        <v>53.24</v>
+        <v>63.56</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -715,7 +715,7 @@
         <v>46183.601388888892</v>
       </c>
       <c r="G10" s="1">
-        <v>49.92</v>
+        <v>64.819999999999993</v>
       </c>
       <c r="H10" s="1">
         <v>0</v>
@@ -741,7 +741,7 @@
         <v>46183.601388888892</v>
       </c>
       <c r="G11" s="1">
-        <v>46.21</v>
+        <v>52.41</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -767,7 +767,7 @@
         <v>46183.601388888892</v>
       </c>
       <c r="G12" s="1">
-        <v>23.82</v>
+        <v>59.62</v>
       </c>
       <c r="H12" s="1">
         <v>0</v>
@@ -793,7 +793,7 @@
         <v>46183.601388888892</v>
       </c>
       <c r="G13" s="1">
-        <v>30.9</v>
+        <v>64.23</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>

--- a/data/daily_measurements.xlsx
+++ b/data/daily_measurements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ruben/dev/duckweed-rmbe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEDD8AE-0B8E-0241-9401-41950F5BF0EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABCE29E-3D5A-764D-ACF9-401B3969515D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14700" yWindow="760" windowWidth="14700" windowHeight="16740" xr2:uid="{1AF4B679-1F14-8444-99BB-B7E1E6DBFAB9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="12">
   <si>
     <t>container_id</t>
   </si>
@@ -455,10 +455,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BBE42C9-4347-6048-B2F8-34461A0CE087}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -796,6 +802,214 @@
         <v>64.23</v>
       </c>
       <c r="H13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>3</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2">
+        <v>46183.601388888892</v>
+      </c>
+      <c r="G14" s="1">
+        <v>73.069999999999993</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>4</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15">
+        <v>3</v>
+      </c>
+      <c r="F15" s="2">
+        <v>46183.601388888892</v>
+      </c>
+      <c r="G15" s="1">
+        <v>70.08</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2">
+        <v>46183.601388888892</v>
+      </c>
+      <c r="G16" s="1">
+        <v>64.150000000000006</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>8</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17" s="2">
+        <v>46183.601388888892</v>
+      </c>
+      <c r="G17" s="1">
+        <v>74.78</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>3</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+      <c r="F18" s="2">
+        <v>46183.601388888892</v>
+      </c>
+      <c r="G18" s="1">
+        <v>54.62</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>4</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19" s="2">
+        <v>46183.601388888892</v>
+      </c>
+      <c r="G19" s="1">
+        <v>72.680000000000007</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>7</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20" s="2">
+        <v>46183.601388888892</v>
+      </c>
+      <c r="G20" s="1">
+        <v>70.08</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>8</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="F21" s="2">
+        <v>46183.601388888892</v>
+      </c>
+      <c r="G21" s="1">
+        <v>73.5</v>
+      </c>
+      <c r="H21" s="1">
         <v>0</v>
       </c>
     </row>

--- a/data/daily_measurements.xlsx
+++ b/data/daily_measurements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ruben/dev/duckweed-rmbe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABCE29E-3D5A-764D-ACF9-401B3969515D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F972452-B9B8-3B48-A7D0-39EB9EA28929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14700" yWindow="760" windowWidth="14700" windowHeight="16740" xr2:uid="{1AF4B679-1F14-8444-99BB-B7E1E6DBFAB9}"/>
   </bookViews>
@@ -929,7 +929,7 @@
         <v>46183.601388888892</v>
       </c>
       <c r="G18" s="1">
-        <v>54.62</v>
+        <v>79.180000000000007</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -955,7 +955,7 @@
         <v>46183.601388888892</v>
       </c>
       <c r="G19" s="1">
-        <v>72.680000000000007</v>
+        <v>81.98</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
@@ -981,7 +981,7 @@
         <v>46183.601388888892</v>
       </c>
       <c r="G20" s="1">
-        <v>70.08</v>
+        <v>89.41</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>46183.601388888892</v>
       </c>
       <c r="G21" s="1">
-        <v>73.5</v>
+        <v>81.36</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>

--- a/data/daily_measurements.xlsx
+++ b/data/daily_measurements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ruben/dev/duckweed-rmbe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F972452-B9B8-3B48-A7D0-39EB9EA28929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D55923-E03B-154E-B914-C64068E0986B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14700" yWindow="760" windowWidth="14700" windowHeight="16740" xr2:uid="{1AF4B679-1F14-8444-99BB-B7E1E6DBFAB9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="12">
   <si>
     <t>container_id</t>
   </si>
@@ -455,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BBE42C9-4347-6048-B2F8-34461A0CE087}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -822,7 +822,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="2">
-        <v>46183.601388888892</v>
+        <v>46184.654861111114</v>
       </c>
       <c r="G14" s="1">
         <v>73.069999999999993</v>
@@ -848,7 +848,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="2">
-        <v>46183.601388888892</v>
+        <v>46184.654861111114</v>
       </c>
       <c r="G15" s="1">
         <v>70.08</v>
@@ -874,7 +874,7 @@
         <v>3</v>
       </c>
       <c r="F16" s="2">
-        <v>46183.601388888892</v>
+        <v>46184.654861111114</v>
       </c>
       <c r="G16" s="1">
         <v>64.150000000000006</v>
@@ -900,7 +900,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="2">
-        <v>46183.601388888892</v>
+        <v>46184.654861111114</v>
       </c>
       <c r="G17" s="1">
         <v>74.78</v>
@@ -926,7 +926,7 @@
         <v>4</v>
       </c>
       <c r="F18" s="2">
-        <v>46183.601388888892</v>
+        <v>46185.626388888886</v>
       </c>
       <c r="G18" s="1">
         <v>79.180000000000007</v>
@@ -952,7 +952,7 @@
         <v>4</v>
       </c>
       <c r="F19" s="2">
-        <v>46183.601388888892</v>
+        <v>46185.626388888886</v>
       </c>
       <c r="G19" s="1">
         <v>81.98</v>
@@ -978,7 +978,7 @@
         <v>4</v>
       </c>
       <c r="F20" s="2">
-        <v>46183.601388888892</v>
+        <v>46185.626388888886</v>
       </c>
       <c r="G20" s="1">
         <v>89.41</v>
@@ -1004,12 +1004,116 @@
         <v>4</v>
       </c>
       <c r="F21" s="2">
-        <v>46183.601388888892</v>
+        <v>46185.626388888886</v>
       </c>
       <c r="G21" s="1">
         <v>81.36</v>
       </c>
       <c r="H21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>3</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>5</v>
+      </c>
+      <c r="F22" s="2">
+        <v>46186.536805555559</v>
+      </c>
+      <c r="G22" s="1">
+        <v>79.12</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>4</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>5</v>
+      </c>
+      <c r="F23" s="2">
+        <v>46187.536805555559</v>
+      </c>
+      <c r="G23" s="1">
+        <v>72.13</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>7</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>5</v>
+      </c>
+      <c r="F24" s="2">
+        <v>46188.536805555559</v>
+      </c>
+      <c r="G24" s="1">
+        <v>74.150000000000006</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>8</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>5</v>
+      </c>
+      <c r="F25" s="2">
+        <v>46189.536805555559</v>
+      </c>
+      <c r="G25" s="1">
+        <v>77.239999999999995</v>
+      </c>
+      <c r="H25" s="1">
         <v>0</v>
       </c>
     </row>

--- a/data/daily_measurements.xlsx
+++ b/data/daily_measurements.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ruben/dev/duckweed-rmbe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D55923-E03B-154E-B914-C64068E0986B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D2CB43-F5DE-AA4B-8A4E-67E87A4A3BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14700" yWindow="760" windowWidth="14700" windowHeight="16740" xr2:uid="{1AF4B679-1F14-8444-99BB-B7E1E6DBFAB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="12">
   <si>
     <t>container_id</t>
   </si>
@@ -81,7 +81,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -91,6 +91,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -117,10 +124,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -455,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BBE42C9-4347-6048-B2F8-34461A0CE087}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -1056,7 +1065,7 @@
         <v>5</v>
       </c>
       <c r="F23" s="2">
-        <v>46187.536805555559</v>
+        <v>46186.536805555559</v>
       </c>
       <c r="G23" s="1">
         <v>72.13</v>
@@ -1082,7 +1091,7 @@
         <v>5</v>
       </c>
       <c r="F24" s="2">
-        <v>46188.536805555559</v>
+        <v>46186.536805555559</v>
       </c>
       <c r="G24" s="1">
         <v>74.150000000000006</v>
@@ -1108,12 +1117,116 @@
         <v>5</v>
       </c>
       <c r="F25" s="2">
-        <v>46189.536805555559</v>
+        <v>46186.536805555559</v>
       </c>
       <c r="G25" s="1">
         <v>77.239999999999995</v>
       </c>
       <c r="H25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>3</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3">
+        <v>7</v>
+      </c>
+      <c r="F26" s="4">
+        <v>46188.644444444442</v>
+      </c>
+      <c r="G26" s="1">
+        <v>90.84</v>
+      </c>
+      <c r="H26" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>4</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" s="3">
+        <v>7</v>
+      </c>
+      <c r="F27" s="4">
+        <v>46188.644444444442</v>
+      </c>
+      <c r="G27" s="1">
+        <v>83.51</v>
+      </c>
+      <c r="H27" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>7</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>7</v>
+      </c>
+      <c r="F28" s="2">
+        <v>46188.668749999997</v>
+      </c>
+      <c r="G28" s="1">
+        <v>86.88</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>8</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29">
+        <v>7</v>
+      </c>
+      <c r="F29" s="4">
+        <v>46188.668749999997</v>
+      </c>
+      <c r="G29" s="1">
+        <v>87.61</v>
+      </c>
+      <c r="H29" s="1">
         <v>0</v>
       </c>
     </row>

--- a/data/daily_measurements.xlsx
+++ b/data/daily_measurements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ruben/dev/duckweed-rmbe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D2CB43-F5DE-AA4B-8A4E-67E87A4A3BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5597888C-66CA-DD49-A29C-DEF6ED49B1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14700" yWindow="760" windowWidth="14700" windowHeight="16740" xr2:uid="{1AF4B679-1F14-8444-99BB-B7E1E6DBFAB9}"/>
   </bookViews>

--- a/data/daily_measurements.xlsx
+++ b/data/daily_measurements.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ruben/dev/duckweed-rmbe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5597888C-66CA-DD49-A29C-DEF6ED49B1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7A7D58-3155-464B-B23B-6D6C495200C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14700" yWindow="760" windowWidth="14700" windowHeight="16740" xr2:uid="{1AF4B679-1F14-8444-99BB-B7E1E6DBFAB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
+    <sheet name="factors" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="16">
   <si>
     <t>container_id</t>
   </si>
@@ -75,6 +76,18 @@
   </si>
   <si>
     <t>low_light</t>
+  </si>
+  <si>
+    <t>container</t>
+  </si>
+  <si>
+    <t>factor</t>
+  </si>
+  <si>
+    <t>before removal</t>
+  </si>
+  <si>
+    <t>after removal</t>
   </si>
 </sst>
 </file>
@@ -124,12 +137,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -464,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BBE42C9-4347-6048-B2F8-34461A0CE087}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -1230,6 +1245,215 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>3</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3">
+        <v>8</v>
+      </c>
+      <c r="F30" s="4">
+        <v>46189.585416666669</v>
+      </c>
+      <c r="G30" s="6">
+        <f>factors!$D$2*50.8</f>
+        <v>101.6</v>
+      </c>
+      <c r="H30" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>4</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="E31" s="3">
+        <v>8</v>
+      </c>
+      <c r="F31" s="4">
+        <v>46189.585416666669</v>
+      </c>
+      <c r="G31" s="1">
+        <f>factors!$D$3*39.76</f>
+        <v>79.52</v>
+      </c>
+      <c r="H31" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>7</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3">
+        <v>8</v>
+      </c>
+      <c r="F32" s="4">
+        <v>46189.585416666669</v>
+      </c>
+      <c r="G32" s="1">
+        <f>factors!$D$4*60.15</f>
+        <v>120.3</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>8</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="3">
+        <v>8</v>
+      </c>
+      <c r="F33" s="4">
+        <v>46189.615972222222</v>
+      </c>
+      <c r="G33" s="1">
+        <f>factors!$D$5*46.25</f>
+        <v>92.5</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D45389-6CB1-FD40-A417-AC4E0F026D13}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>90.84</v>
+      </c>
+      <c r="C2">
+        <v>34.22</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="5">
+        <f>B2/C2</f>
+        <v>2.6545879602571598</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>83.51</v>
+      </c>
+      <c r="C3">
+        <v>31.22</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5">
+        <f>B3/C3</f>
+        <v>2.6748878923766819</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>86.88</v>
+      </c>
+      <c r="C4">
+        <v>33.14</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5">
+        <f>B4/C4</f>
+        <v>2.6216053108026554</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>87.61</v>
+      </c>
+      <c r="C5">
+        <v>44.99</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="5">
+        <f>B5/C5</f>
+        <v>1.9473216270282283</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/data/daily_measurements.xlsx
+++ b/data/daily_measurements.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ruben/dev/duckweed-rmbe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E7A7D58-3155-464B-B23B-6D6C495200C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1FABF1-FB87-9B45-B808-BE324C3D4D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14700" yWindow="760" windowWidth="14700" windowHeight="16740" xr2:uid="{1AF4B679-1F14-8444-99BB-B7E1E6DBFAB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
-    <sheet name="factors" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="12">
   <si>
     <t>container_id</t>
   </si>
@@ -76,18 +75,6 @@
   </si>
   <si>
     <t>low_light</t>
-  </si>
-  <si>
-    <t>container</t>
-  </si>
-  <si>
-    <t>factor</t>
-  </si>
-  <si>
-    <t>before removal</t>
-  </si>
-  <si>
-    <t>after removal</t>
   </si>
 </sst>
 </file>
@@ -137,13 +124,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -479,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BBE42C9-4347-6048-B2F8-34461A0CE087}">
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -1264,8 +1250,8 @@
       <c r="F30" s="4">
         <v>46189.585416666669</v>
       </c>
-      <c r="G30" s="6">
-        <f>factors!$D$2*50.8</f>
+      <c r="G30" s="5">
+        <f>2*50.8</f>
         <v>101.6</v>
       </c>
       <c r="H30" s="1">
@@ -1292,7 +1278,7 @@
         <v>46189.585416666669</v>
       </c>
       <c r="G31" s="1">
-        <f>factors!$D$3*39.76</f>
+        <f>2*39.76</f>
         <v>79.52</v>
       </c>
       <c r="H31" s="1">
@@ -1319,7 +1305,7 @@
         <v>46189.585416666669</v>
       </c>
       <c r="G32" s="1">
-        <f>factors!$D$4*60.15</f>
+        <f>2*60.15</f>
         <v>120.3</v>
       </c>
       <c r="H32" s="1">
@@ -1346,112 +1332,119 @@
         <v>46189.615972222222</v>
       </c>
       <c r="G33" s="1">
-        <f>factors!$D$5*46.25</f>
-        <v>92.5</v>
+        <f>2*46.26</f>
+        <v>92.52</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D45389-6CB1-FD40-A417-AC4E0F026D13}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>90.84</v>
-      </c>
-      <c r="C2">
-        <v>34.22</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2" s="5">
-        <f>B2/C2</f>
-        <v>2.6545879602571598</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>3</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3">
+        <v>9</v>
+      </c>
+      <c r="F34" s="4">
+        <v>46190.590277777781</v>
+      </c>
+      <c r="G34" s="5">
+        <f>2*54.91</f>
+        <v>109.82</v>
+      </c>
+      <c r="H34" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
         <v>4</v>
       </c>
-      <c r="B3">
-        <v>83.51</v>
-      </c>
-      <c r="C3">
-        <v>31.22</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="5">
-        <f>B3/C3</f>
-        <v>2.6748878923766819</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="B35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" s="3">
+        <v>9</v>
+      </c>
+      <c r="F35" s="4">
+        <v>46190.590277777781</v>
+      </c>
+      <c r="G35" s="1">
+        <f>2*42.87</f>
+        <v>85.74</v>
+      </c>
+      <c r="H35" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
         <v>7</v>
       </c>
-      <c r="B4">
-        <v>86.88</v>
-      </c>
-      <c r="C4">
-        <v>33.14</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4" s="5">
-        <f>B4/C4</f>
-        <v>2.6216053108026554</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>87.61</v>
-      </c>
-      <c r="C5">
-        <v>44.99</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5" s="5">
-        <f>B5/C5</f>
-        <v>1.9473216270282283</v>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="3">
+        <v>9</v>
+      </c>
+      <c r="F36" s="4">
+        <v>46190.590277777781</v>
+      </c>
+      <c r="G36" s="1">
+        <f>2*51.01</f>
+        <v>102.02</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>8</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" s="3">
+        <v>9</v>
+      </c>
+      <c r="F37" s="4">
+        <v>46190.590277777781</v>
+      </c>
+      <c r="G37" s="1">
+        <f>2*58.68</f>
+        <v>117.36</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/daily_measurements.xlsx
+++ b/data/daily_measurements.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ruben/dev/duckweed-rmbe/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1FABF1-FB87-9B45-B808-BE324C3D4D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9C4881-D43D-EF40-A434-F9EDBAABA446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14700" yWindow="760" windowWidth="14700" windowHeight="16740" xr2:uid="{1AF4B679-1F14-8444-99BB-B7E1E6DBFAB9}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="14700" windowHeight="16740" xr2:uid="{1AF4B679-1F14-8444-99BB-B7E1E6DBFAB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
+    <sheet name="factors" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="16">
   <si>
     <t>container_id</t>
   </si>
@@ -75,6 +76,18 @@
   </si>
   <si>
     <t>low_light</t>
+  </si>
+  <si>
+    <t>container</t>
+  </si>
+  <si>
+    <t>before removal</t>
+  </si>
+  <si>
+    <t>after removal</t>
+  </si>
+  <si>
+    <t>factor</t>
   </si>
 </sst>
 </file>
@@ -124,13 +137,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="22" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standaard" xfId="0" builtinId="0"/>
@@ -534,7 +548,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
@@ -560,7 +574,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>11</v>
@@ -638,7 +652,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>9</v>
@@ -664,7 +678,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>11</v>
@@ -742,7 +756,7 @@
         <v>4</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>9</v>
@@ -768,7 +782,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>11</v>
@@ -846,7 +860,7 @@
         <v>4</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>9</v>
@@ -872,7 +886,7 @@
         <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>11</v>
@@ -950,7 +964,7 @@
         <v>4</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>9</v>
@@ -976,7 +990,7 @@
         <v>7</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>11</v>
@@ -1054,7 +1068,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>9</v>
@@ -1080,7 +1094,7 @@
         <v>7</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>11</v>
@@ -1158,7 +1172,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>9</v>
@@ -1184,7 +1198,7 @@
         <v>7</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>11</v>
@@ -1251,8 +1265,8 @@
         <v>46189.585416666669</v>
       </c>
       <c r="G30" s="5">
-        <f>2*50.8</f>
-        <v>101.6</v>
+        <f>factors!$D$2*50.8</f>
+        <v>134.85306838106371</v>
       </c>
       <c r="H30" s="1">
         <v>2</v>
@@ -1263,7 +1277,7 @@
         <v>4</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>9</v>
@@ -1277,9 +1291,9 @@
       <c r="F31" s="4">
         <v>46189.585416666669</v>
       </c>
-      <c r="G31" s="1">
-        <f>2*39.76</f>
-        <v>79.52</v>
+      <c r="G31" s="5">
+        <f>factors!$D$3*39.76</f>
+        <v>106.35354260089687</v>
       </c>
       <c r="H31" s="1">
         <v>2</v>
@@ -1290,7 +1304,7 @@
         <v>7</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>11</v>
@@ -1304,9 +1318,9 @@
       <c r="F32" s="4">
         <v>46189.585416666669</v>
       </c>
-      <c r="G32" s="1">
-        <f>2*60.15</f>
-        <v>120.3</v>
+      <c r="G32" s="5">
+        <f>factors!$D$4*60.15</f>
+        <v>157.68955944477972</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -1331,9 +1345,9 @@
       <c r="F33" s="4">
         <v>46189.615972222222</v>
       </c>
-      <c r="G33" s="1">
-        <f>2*46.26</f>
-        <v>92.52</v>
+      <c r="G33" s="5">
+        <f>factors!$D$5*46.26</f>
+        <v>90.083098466325836</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
@@ -1359,8 +1373,8 @@
         <v>46190.590277777781</v>
       </c>
       <c r="G34" s="5">
-        <f>2*54.91</f>
-        <v>109.82</v>
+        <f>factors!$D$2*54.91</f>
+        <v>145.76342489772063</v>
       </c>
       <c r="H34" s="1">
         <v>3</v>
@@ -1371,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>9</v>
@@ -1385,9 +1399,9 @@
       <c r="F35" s="4">
         <v>46190.590277777781</v>
       </c>
-      <c r="G35" s="1">
-        <f>2*42.87</f>
-        <v>85.74</v>
+      <c r="G35" s="5">
+        <f>factors!$D$3*42.87</f>
+        <v>114.67244394618835</v>
       </c>
       <c r="H35" s="1">
         <v>3</v>
@@ -1398,7 +1412,7 @@
         <v>7</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>11</v>
@@ -1412,9 +1426,9 @@
       <c r="F36" s="4">
         <v>46190.590277777781</v>
       </c>
-      <c r="G36" s="1">
-        <f>2*51.01</f>
-        <v>102.02</v>
+      <c r="G36" s="5">
+        <f>factors!$D$4*51.01</f>
+        <v>133.72808690404344</v>
       </c>
       <c r="H36" s="1">
         <v>0</v>
@@ -1439,9 +1453,9 @@
       <c r="F37" s="4">
         <v>46190.590277777781</v>
       </c>
-      <c r="G37" s="1">
-        <f>2*58.68</f>
-        <v>117.36</v>
+      <c r="G37" s="5">
+        <f>factors!$D$5*58.68</f>
+        <v>114.26883307401644</v>
       </c>
       <c r="H37" s="1">
         <v>0</v>
@@ -1451,4 +1465,93 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00CF138E-3B1C-8A41-B1EC-E31311D94D0C}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>90.84</v>
+      </c>
+      <c r="C2">
+        <v>34.22</v>
+      </c>
+      <c r="D2" s="6">
+        <f>B2/C2</f>
+        <v>2.6545879602571598</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>83.51</v>
+      </c>
+      <c r="C3">
+        <v>31.22</v>
+      </c>
+      <c r="D3" s="6">
+        <f t="shared" ref="D3:D5" si="0">B3/C3</f>
+        <v>2.6748878923766819</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>86.88</v>
+      </c>
+      <c r="C4">
+        <v>33.14</v>
+      </c>
+      <c r="D4" s="6">
+        <f t="shared" si="0"/>
+        <v>2.6216053108026554</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>87.61</v>
+      </c>
+      <c r="C5">
+        <v>44.99</v>
+      </c>
+      <c r="D5" s="6">
+        <f t="shared" si="0"/>
+        <v>1.9473216270282283</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>